--- a/reports/jobs_2026-07-22.xlsx
+++ b/reports/jobs_2026-07-22.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Job Openings" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Openings'!$A$1:$I$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Openings'!$A$1:$I$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -496,17 +496,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SAP FICO Consultant in UAE</t>
+          <t>Accountant in UAE - WITH 2 YEARS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SAP FICO Lead — Finance Systems</t>
+          <t>Accountant (2–3 Years Experience</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Black &amp; Grey HR Consultancy FZE</t>
+          <t>SAVE IN GOLD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -527,12 +527,12 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Trabajo.org</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://ae.trabajo.org/job-3339-3876bcfb2f52231b95ff2dd9bde14364</t>
+          <t>https://ae.indeed.com/viewjob?jk=c4c2652e11827e63</t>
         </is>
       </c>
     </row>
@@ -544,12 +544,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Accountant (2–3 Years Experience</t>
+          <t>R2R Accountant: IFRS, SAP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SAVE IN GOLD</t>
+          <t>AlFuttaim</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -570,12 +570,12 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>Trabajo.org</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://ae.indeed.com/viewjob?jk=c4c2652e11827e63</t>
+          <t>https://ae.trabajo.org/job-3988-8c10f6bc7a5910ef3132c57e2847b664</t>
         </is>
       </c>
     </row>
@@ -587,12 +587,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R2R Accountant: IFRS, SAP</t>
+          <t>Dubai Accountant: IFRS, Budgeting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AlFuttaim</t>
+          <t>NADIA Recruitment &amp; Management Consultants</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://ae.trabajo.org/job-3988-8c10f6bc7a5910ef3132c57e2847b664</t>
+          <t>https://ae.trabajo.org/job-3988-3a4b0f07db97228837a866bbf4d18cd3</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dubai Accountant: IFRS, Budgeting</t>
+          <t>Shipping Agency Accountant — Immediate Start Preferred</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NADIA Recruitment &amp; Management Consultants</t>
+          <t>Gulfjobfair</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -656,12 +656,12 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Trabajo.org</t>
+          <t>Jooble</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://ae.trabajo.org/job-3988-3a4b0f07db97228837a866bbf4d18cd3</t>
+          <t>https://ae.jooble.org/jdp/-6462434079937302740</t>
         </is>
       </c>
     </row>
@@ -673,12 +673,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shipping Agency Accountant — Immediate Start Preferred</t>
+          <t>Senior Accountant: Global Close, Consolidation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gulfjobfair</t>
+          <t>McDermott International, Ltd</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -699,12 +699,12 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Jooble</t>
+          <t>Trabajo.org</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://ae.jooble.org/jdp/-6462434079937302740</t>
+          <t>https://ae.trabajo.org/job-3339-fb03e4817ab4d93273186fea8dd4d0db</t>
         </is>
       </c>
     </row>
@@ -716,12 +716,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Senior Accountant: Global Close, Consolidation</t>
+          <t>M.Com Accountant: Import/Export</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>McDermott International, Ltd</t>
+          <t>BOSCO Aluminium and Glass</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://ae.trabajo.org/job-3339-fb03e4817ab4d93273186fea8dd4d0db</t>
+          <t>https://ae.trabajo.org/job-3339-ee15b461ed8f85520c2090dc9f83f946</t>
         </is>
       </c>
     </row>
@@ -759,12 +759,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M.Com Accountant: Import/Export</t>
+          <t>Remote UAE Junior Accountant</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BOSCO Aluminium and Glass</t>
+          <t>Huzzle</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://ae.trabajo.org/job-3339-ee15b461ed8f85520c2090dc9f83f946</t>
+          <t>https://ae.trabajo.org/job-3339-a83075df408cb56d0aeede3099eedc0b</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Remote UAE Junior Accountant</t>
+          <t>Junior Accountant – Global SSC, IFRS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Huzzle</t>
+          <t>IFZA Dubai</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://ae.trabajo.org/job-3339-a83075df408cb56d0aeede3099eedc0b</t>
+          <t>https://ae.trabajo.org/job-3339-ab9a582ee36b326c7b24c9c98574fce2</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UAE Accountant | Financial Reporting</t>
+          <t>Excel-Savvy Accountant for Precise Financial Control</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ds Light</t>
+          <t>NADIA Recruitment &amp; Management Consultants</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://ae.trabajo.org/job-3339-0d843153a67c8cf96bfb10be7611ceb7</t>
+          <t>https://ae.trabajo.org/job-3339-c4f5c6bff8bdbc332ee38149fc69379f</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Junior Accountant: Data Entry</t>
+          <t>Dubai Financial Accountant: Month-End</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BRAVACASA INTERIOR LLC</t>
+          <t>applydubaijob.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -919,34 +919,34 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://ae.trabajo.org/job-3339-ee0f97d71449137d2571c78ac9c88a52</t>
+          <t>https://ae.trabajo.org/job-3988-d4b95cc4aa3f3b8cbe1c86bdb3a69287</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Accountant in UAE - WITH 2 YEARS</t>
+          <t>NEW SAP JOBS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Junior Accountant – Global SSC, IFRS</t>
+          <t>SAP Functional Analyst</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IFZA Dubai</t>
+          <t>Integration International Inc.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>Washington, US</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Contractor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -954,15 +954,19 @@
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 50 - 55</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Trabajo.org</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://ae.trabajo.org/job-3339-ab9a582ee36b326c7b24c9c98574fce2</t>
+          <t>https://www.linkedin.com/jobs/view/sap-functional-analyst-at-integration-international-inc-4443545130</t>
         </is>
       </c>
     </row>
@@ -974,12 +978,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SAP Functional Analyst</t>
+          <t>SAP BTP Lead</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Integration International Inc.</t>
+          <t>Inherent Technologies</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -989,7 +993,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Contractor</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -997,11 +1001,7 @@
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 50 - 55</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>LinkedIn</t>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/sap-functional-analyst-at-integration-international-inc-4443545130</t>
+          <t>https://www.linkedin.com/jobs/view/sap-btp-lead-at-inherent-technologies-4443545395</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SAP BTP Lead</t>
+          <t>SAP Data Migration &amp; Conversion Transformation Consultant</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Inherent Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/sap-btp-lead-at-inherent-technologies-4443545395</t>
+          <t>https://www.linkedin.com/jobs/view/sap-data-migration-conversion-transformation-consultant-at-deloitte-4443595696</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SAP Data Migration &amp; Conversion Transformation Consultant</t>
+          <t>Senior SAP ABAP Developer (Open to Remote)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bertelsmann-Jobs</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Washington, US</t>
+          <t>Westminster, US</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1084,18 +1084,18 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Smart Recruiters Jobs</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/sap-data-migration-conversion-transformation-consultant-at-deloitte-4443595696</t>
+          <t>https://jobs.smartrecruiters.com/Bertelsmann-Jobs/744000138864160-senior-sap-abap-developer-open-to-remote-</t>
         </is>
       </c>
     </row>
@@ -1107,22 +1107,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Senior SAP ABAP Developer (Open to Remote)</t>
+          <t>Senior SAP Basis Migration Specialist with S/4HANA Private Cloud Expertise</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bertelsmann-Jobs</t>
+          <t>Trigyn Technologies, Inc.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Westminster, US</t>
+          <t>New York, US</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Contractor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1133,12 +1133,12 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Smart Recruiters Jobs</t>
+          <t>Dice</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/Bertelsmann-Jobs/744000138864160-senior-sap-abap-developer-open-to-remote-</t>
+          <t>https://www.dice.com/job-detail/0c84fcf6-4033-45ad-be3a-ff22fa0316f1</t>
         </is>
       </c>
     </row>
@@ -1150,17 +1150,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SAP CS  Service management Lead Architect</t>
+          <t>SAP S/4HANA Treasury Migration Consultant</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Prudent Technologies and Consulting, Inc.</t>
+          <t>LingaTech</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Harrisburg, US</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/sap-cs-service-management-lead-architect-at-prudent-technologies-and-consulting-inc-4440296117</t>
+          <t>https://www.linkedin.com/jobs/view/sap-s-4hana-treasury-migration-consultant-at-lingatech-4443557005</t>
         </is>
       </c>
     </row>
@@ -1236,17 +1236,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SAP FI/CO Analyst - Hybrid</t>
+          <t>SAP AI Leader (Joule BTP)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Liberty Personnel Services, Inc.</t>
+          <t>NTT DATA Services</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Wilmington, US</t>
+          <t>Remote, US</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1256,18 +1256,18 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>ZipRecruiter</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/sap-fi-co-analyst-hybrid-at-liberty-personnel-services-inc-4442902669</t>
+          <t>https://www.ziprecruiter.com/c/NTT-DATA-Services/Job/SAP-AI-Leader-(Joule-BTP)/-in-Remote,US?jid=81bab3932525f4b4</t>
         </is>
       </c>
     </row>
@@ -1322,27 +1322,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SAP S/4HANA Treasury Migration Consultant</t>
+          <t>SAP P2P – Senior Consultant</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LingaTech</t>
+          <t>Globalwave Softech Pvt Ltd</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Harrisburg, US</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Contractor</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1353,55 +1353,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/sap-s-4hana-treasury-migration-consultant-at-lingatech-4443557005</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>NEW SAP JOBS</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>SAP Sales Executive</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Inoltra</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>New York, US</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/sap-sales-executive-at-inoltra-4443522649</t>
+          <t>https://www.linkedin.com/jobs/view/sap-p2p-%E2%80%93-senior-consultant-at-globalwave-softech-pvt-ltd-4442959035</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I22"/>
+  <autoFilter ref="A1:I21"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
@@ -1423,7 +1380,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
